--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/03_PPC3 - Güvenli Lansman ve Güçlendirilmiş Kontrol/EKG-KLT-PLN-02_guvenli_lansman_plani__tris.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/03_PPC3 - Güvenli Lansman ve Güçlendirilmiş Kontrol/EKG-KLT-PLN-02_guvenli_lansman_plani__tris.xlsx
@@ -1014,7 +1014,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Güvenli Lansman Planı - TRIS</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 03.09.2026
+Revizyon nedeni: TRIS kapsamı ve müşteri çıkış şartları korundu; uygunsuz oranına tam sayı ve miktar tutarlılığı eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbba64713b0c94207"/>
   <x:tableParts count="1">
@@ -1386,7 +1387,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Güvenli Lansman Planı - TRIS</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 03.09.2026
+Revizyon nedeni: TRIS kapsamı ve müşteri çıkış şartları korundu; uygunsuz oranına tam sayı ve miktar tutarlılığı eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R215c24ac7acf4941"/>
   <x:tableParts count="1">
@@ -1760,7 +1762,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Güvenli Lansman Planı - TRIS</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 03.09.2026
+Revizyon nedeni: TRIS kapsamı ve müşteri çıkış şartları korundu; uygunsuz oranına tam sayı ve miktar tutarlılığı eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6950b3b89cf34f94"/>
   <x:tableParts count="1">
@@ -2189,7 +2192,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Güvenli Lansman Planı - TRIS</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 03.09.2026
+Revizyon nedeni: TRIS kapsamı ve müşteri çıkış şartları korundu; uygunsuz oranına tam sayı ve miktar tutarlılığı eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b5bb22c97d34dda"/>
   <x:tableParts count="1">
